--- a/downloads/assam.xlsx
+++ b/downloads/assam.xlsx
@@ -9,15 +9,16 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Every Assam figure with its sou" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State figures" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules beside the SIR's" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NRC lists of 2019" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D-voters" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Foreigners Tribunals" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detention, state" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detention centres" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rolls by seat and sex" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State figures" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules beside the SIR's" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NRC lists of 2019" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D-voters" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Foreigners Tribunals" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detention, state" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detention centres" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -543,7 +544,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>State figures</t>
+          <t>Rolls by seat and sex</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -553,15 +554,15 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>constituency</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Every roll figure, as quoted by the press.</t>
+          <t>The Chief Electoral Officer's tables of the final roll of 8 February 2024, the draft and the final roll, every constituency by sex.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr"/>
@@ -574,7 +575,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Rules beside the SIR's</t>
+          <t>State figures</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -588,11 +589,11 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Each rule of the Special Revision set against the SIR's.</t>
+          <t>Every roll figure, as quoted by the press.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr"/>
@@ -605,7 +606,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Rules beside the SIR's</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -619,11 +620,11 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>The order's schedule.</t>
+          <t>Each rule of the Special Revision set against the SIR's.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
@@ -636,7 +637,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>NRC lists of 2019</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -650,11 +651,11 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>The figures of the lists published on 31 August 2019.</t>
+          <t>The order's schedule.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr"/>
@@ -667,7 +668,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>D-voters</t>
+          <t>NRC lists of 2019</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -681,11 +682,11 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Answers in Parliament on D-voters.</t>
+          <t>The figures of the lists published on 31 August 2019.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr"/>
@@ -698,7 +699,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Foreigners Tribunals</t>
+          <t>D-voters</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -712,11 +713,11 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Answers in Parliament on the Foreigners Tribunals.</t>
+          <t>Answers in Parliament on D-voters.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr"/>
@@ -729,7 +730,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Detention, state</t>
+          <t>Foreigners Tribunals</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -743,11 +744,11 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Answers in Parliament on detention.</t>
+          <t>Answers in Parliament on the Foreigners Tribunals.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr"/>
@@ -760,7 +761,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Detention centres</t>
+          <t>Detention, state</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -774,15 +775,46 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Capacity and inmates by centre.</t>
+          <t>Answers in Parliament on detention.</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>in this workbook only</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Detention centres</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Source table</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Capacity and inmates by centre.</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>in this workbook only</t>
         </is>
@@ -794,6 +826,329 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>page_or_para</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>detention_centres_2019</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Lok Sabha USQ 2340, 03.12.2019, MHA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>inmates_total_20191128</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>970</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Lok Sabha USQ 2340, 03.12.2019, MHA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>table, Total row</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>inmates_men_20191128</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>646</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Total row</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>inmates_women_20191128</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>324</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Total row</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>capacity_total_2020</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3331</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Lok Sabha USQ 3880, 17.03.2020, MHA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>answer, Total row</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>matia_goalpara_capacity_under_construction_2020</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Lok Sabha USQ 3880, 17.03.2020, MHA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>answer page 2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>inmates_died_20190301_20200229</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Lok Sabha USQ 3880, 17.03.2020, MHA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>answer page 2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>declared_foreigners_over_3_years_in_detention_2019</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>181</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Lok Sabha USQ 3561, 10.12.2019, MHA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>answer (a)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>convicted_foreigners_over_3_years_in_detention_2019</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>44</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>answer (a)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>declared_foreigners_detained_in_2019</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>289</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>answer (b)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>released_after_3_years_per_sc_10052019</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>128</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>answer (d)&amp;(e)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -955,13 +1310,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1091,568 +1446,568 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>State figures</t>
+          <t>Rolls by seat and sex</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>ac</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What the row measures.</t>
+          <t>Assembly constituency number.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>State figures</t>
+          <t>Rolls by seat and sex</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>ac_name</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The figure.</t>
+          <t>Assembly constituency name, as the source spells it.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>State figures</t>
+          <t>Rolls by seat and sex</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>The document the figure comes from.</t>
+          <t>SC or ST where the seat is reserved, and blank otherwise.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rules beside the SIR's</t>
+          <t>Rolls by seat and sex</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>aspect</t>
+          <t>district</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rule compared.</t>
+          <t>District.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rules beside the SIR's</t>
+          <t>Rolls by seat and sex</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>assam_special_revision</t>
+          <t>men_2024</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The rule in Assam's Special Revision.</t>
+          <t>Men on the final roll of 8 February 2024.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rules beside the SIR's</t>
+          <t>Rolls by seat and sex</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>assam_source</t>
+          <t>women_2024</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Document for the Assam rule.</t>
+          <t>Women on the final roll of 8 February 2024.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rules beside the SIR's</t>
+          <t>Rolls by seat and sex</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>assam_para</t>
+          <t>third_2024</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Paragraph for the Assam rule.</t>
+          <t>Third-gender electors on the final roll of 8 February 2024.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rules beside the SIR's</t>
+          <t>Rolls by seat and sex</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>assam_quote</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Words of the Assam order.</t>
+          <t>All electors on the final roll of 8 February 2024.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rules beside the SIR's</t>
+          <t>Rolls by seat and sex</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sir_phase2</t>
+          <t>polling_stations</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>The rule in the SIR order of 27 October 2025.</t>
+          <t>Polling stations.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rules beside the SIR's</t>
+          <t>Rolls by seat and sex</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sir_source</t>
+          <t>men_draft</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Document for the SIR rule.</t>
+          <t>Men on the draft roll of 27 December 2025.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Rolls by seat and sex</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>women_draft</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Step of the schedule.</t>
+          <t>Women on the draft roll of 27 December 2025.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Rolls by seat and sex</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>activity</t>
+          <t>third_draft</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What happens at the step.</t>
+          <t>Third-gender electors on the draft roll of 27 December 2025.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Rolls by seat and sex</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>from</t>
+          <t>total_draft</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Start date.</t>
+          <t>All electors on the draft roll of 27 December 2025.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Rolls by seat and sex</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>men_final</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>End date.</t>
+          <t>Men on the final roll of 10 February 2026.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Rolls by seat and sex</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>para</t>
+          <t>women_final</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Paragraph of the order.</t>
+          <t>Women on the final roll of 10 February 2026.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Rolls by seat and sex</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>third_final</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>The document the figure comes from.</t>
+          <t>Third-gender electors on the final roll of 10 February 2026.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NRC lists of 2019</t>
+          <t>Rolls by seat and sex</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>total_final</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>What the row measures.</t>
+          <t>All electors on the final roll of 10 February 2026.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NRC lists of 2019</t>
+          <t>State figures</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>item</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>The figure.</t>
+          <t>What the row measures.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NRC lists of 2019</t>
+          <t>State figures</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>value</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>The document the figure comes from.</t>
+          <t>The figure.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NRC lists of 2019</t>
+          <t>State figures</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>page_or_para</t>
+          <t>source</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Page or paragraph of the source.</t>
+          <t>The document the figure comes from.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NRC lists of 2019</t>
+          <t>Rules beside the SIR's</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>aspect</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes if the source is a primary document.</t>
+          <t>Rule compared.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>D-voters</t>
+          <t>Rules beside the SIR's</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>as_of</t>
+          <t>assam_special_revision</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Date the figure refers to.</t>
+          <t>The rule in Assam's Special Revision.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>D-voters</t>
+          <t>Rules beside the SIR's</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>d_voters</t>
+          <t>assam_source</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>D-voters (doubtful voters).</t>
+          <t>Document for the Assam rule.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>D-voters</t>
+          <t>Rules beside the SIR's</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>d_voters_women</t>
+          <t>assam_para</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>D-voters who are women.</t>
+          <t>Paragraph for the Assam rule.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>D-voters</t>
+          <t>Rules beside the SIR's</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>assam_quote</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>The document the figure comes from.</t>
+          <t>Words of the Assam order.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>D-voters</t>
+          <t>Rules beside the SIR's</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>page_or_para</t>
+          <t>sir_phase2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Page or paragraph of the source.</t>
+          <t>The rule in the SIR order of 27 October 2025.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>D-voters</t>
+          <t>Rules beside the SIR's</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>sir_source</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yes if the source is a primary document.</t>
+          <t>Document for the SIR rule.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Foreigners Tribunals</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>as_of</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Date the figure refers to.</t>
+          <t>Step of the schedule.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Foreigners Tribunals</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>activity</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>What the row measures.</t>
+          <t>What happens at the step.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Foreigners Tribunals</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>from</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>The figure.</t>
+          <t>Start date.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Foreigners Tribunals</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>to</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>The document the figure comes from.</t>
+          <t>End date.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Foreigners Tribunals</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>page_or_para</t>
+          <t>para</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Page or paragraph of the source.</t>
+          <t>Paragraph of the order.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Foreigners Tribunals</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>source</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Yes if the source is a primary document.</t>
+          <t>The document the figure comes from.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Detention, state</t>
+          <t>NRC lists of 2019</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1669,7 +2024,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Detention, state</t>
+          <t>NRC lists of 2019</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1686,7 +2041,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Detention, state</t>
+          <t>NRC lists of 2019</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1703,7 +2058,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Detention, state</t>
+          <t>NRC lists of 2019</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1720,7 +2075,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Detention, state</t>
+          <t>NRC lists of 2019</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1737,83 +2092,372 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Detention centres</t>
+          <t>D-voters</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>centre</t>
+          <t>as_of</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Detention centre.</t>
+          <t>Date the figure refers to.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Detention centres</t>
+          <t>D-voters</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>capacity_2020</t>
+          <t>d_voters</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Capacity in 2020.</t>
+          <t>D-voters (doubtful voters).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Detention centres</t>
+          <t>D-voters</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>inmates_men_20191128</t>
+          <t>d_voters_women</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Inmates, men, 28 November 2019.</t>
+          <t>D-voters who are women.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Detention centres</t>
+          <t>D-voters</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>inmates_women_20191128</t>
+          <t>source</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inmates, women, 28 November 2019.</t>
+          <t>The document the figure comes from.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>D-voters</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>page_or_para</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Page or paragraph of the source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>D-voters</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Yes if the source is a primary document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Foreigners Tribunals</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>as_of</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Date the figure refers to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Foreigners Tribunals</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>What the row measures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Foreigners Tribunals</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>The figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Foreigners Tribunals</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>The document the figure comes from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Foreigners Tribunals</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>page_or_para</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Page or paragraph of the source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Foreigners Tribunals</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Yes if the source is a primary document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Detention, state</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>What the row measures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Detention, state</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>The figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Detention, state</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>The document the figure comes from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Detention, state</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>page_or_para</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Page or paragraph of the source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Detention, state</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Yes if the source is a primary document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>Detention centres</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>centre</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Detention centre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Detention centres</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>capacity_2020</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Capacity in 2020.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Detention centres</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>inmates_men_20191128</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Inmates, men, 28 November 2019.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Detention centres</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>inmates_women_20191128</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Inmates, women, 28 November 2019.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Detention centres</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
         <is>
           <t>inmates_total_20191128</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Inmates, 28 November 2019.</t>
         </is>
@@ -4722,6 +5366,7070 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Q127"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ac</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>ac_name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>men_2024</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>women_2024</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>third_2024</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>total_2024</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>polling_stations</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>men_draft</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>women_draft</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>third_draft</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>total_draft</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>men_final</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>women_final</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>third_final</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>total_final</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Gossaigaon</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kokrajhar</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>57073</v>
+      </c>
+      <c r="F2" t="n">
+        <v>56209</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>113282</v>
+      </c>
+      <c r="I2" t="n">
+        <v>154</v>
+      </c>
+      <c r="J2" t="n">
+        <v>58021</v>
+      </c>
+      <c r="K2" t="n">
+        <v>57849</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M2" t="n">
+        <v>115874</v>
+      </c>
+      <c r="N2" t="n">
+        <v>57469</v>
+      </c>
+      <c r="O2" t="n">
+        <v>57012</v>
+      </c>
+      <c r="P2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>114486</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dotma</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Kokrajhar</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>52088</v>
+      </c>
+      <c r="F3" t="n">
+        <v>52855</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>104943</v>
+      </c>
+      <c r="I3" t="n">
+        <v>146</v>
+      </c>
+      <c r="J3" t="n">
+        <v>54066</v>
+      </c>
+      <c r="K3" t="n">
+        <v>54886</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>108952</v>
+      </c>
+      <c r="N3" t="n">
+        <v>53180</v>
+      </c>
+      <c r="O3" t="n">
+        <v>53831</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>107011</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kokrajhar</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Kokrajhar</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>69331</v>
+      </c>
+      <c r="F4" t="n">
+        <v>71849</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>141181</v>
+      </c>
+      <c r="I4" t="n">
+        <v>190</v>
+      </c>
+      <c r="J4" t="n">
+        <v>72235</v>
+      </c>
+      <c r="K4" t="n">
+        <v>74864</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>147102</v>
+      </c>
+      <c r="N4" t="n">
+        <v>70968</v>
+      </c>
+      <c r="O4" t="n">
+        <v>73273</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>144241</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Baokhungri</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Kokrajhar</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>79604</v>
+      </c>
+      <c r="F5" t="n">
+        <v>79909</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>159514</v>
+      </c>
+      <c r="I5" t="n">
+        <v>223</v>
+      </c>
+      <c r="J5" t="n">
+        <v>82824</v>
+      </c>
+      <c r="K5" t="n">
+        <v>83454</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>166279</v>
+      </c>
+      <c r="N5" t="n">
+        <v>81865</v>
+      </c>
+      <c r="O5" t="n">
+        <v>82448</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>164314</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Parbatjhora</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Kokrajhar</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>85992</v>
+      </c>
+      <c r="F6" t="n">
+        <v>82259</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>168252</v>
+      </c>
+      <c r="I6" t="n">
+        <v>231</v>
+      </c>
+      <c r="J6" t="n">
+        <v>89432</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84969</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>174402</v>
+      </c>
+      <c r="N6" t="n">
+        <v>89298</v>
+      </c>
+      <c r="O6" t="n">
+        <v>84872</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>174173</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Golakganj</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Dhubri</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>104697</v>
+      </c>
+      <c r="F7" t="n">
+        <v>98182</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>202881</v>
+      </c>
+      <c r="I7" t="n">
+        <v>260</v>
+      </c>
+      <c r="J7" t="n">
+        <v>106320</v>
+      </c>
+      <c r="K7" t="n">
+        <v>99477</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>205797</v>
+      </c>
+      <c r="N7" t="n">
+        <v>106078</v>
+      </c>
+      <c r="O7" t="n">
+        <v>97798</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>203876</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Gauripur</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Dhubri</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>151756</v>
+      </c>
+      <c r="F8" t="n">
+        <v>141839</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>293598</v>
+      </c>
+      <c r="I8" t="n">
+        <v>384</v>
+      </c>
+      <c r="J8" t="n">
+        <v>157057</v>
+      </c>
+      <c r="K8" t="n">
+        <v>146084</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>303145</v>
+      </c>
+      <c r="N8" t="n">
+        <v>160628</v>
+      </c>
+      <c r="O8" t="n">
+        <v>149962</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>310594</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dhubri</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Dhubri</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>116178</v>
+      </c>
+      <c r="F9" t="n">
+        <v>110004</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>226185</v>
+      </c>
+      <c r="I9" t="n">
+        <v>296</v>
+      </c>
+      <c r="J9" t="n">
+        <v>119128</v>
+      </c>
+      <c r="K9" t="n">
+        <v>112030</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>231161</v>
+      </c>
+      <c r="N9" t="n">
+        <v>119493</v>
+      </c>
+      <c r="O9" t="n">
+        <v>111642</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>231136</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Birsing-Jarua</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Dhubri</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>136908</v>
+      </c>
+      <c r="F10" t="n">
+        <v>129873</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>266781</v>
+      </c>
+      <c r="I10" t="n">
+        <v>354</v>
+      </c>
+      <c r="J10" t="n">
+        <v>141900</v>
+      </c>
+      <c r="K10" t="n">
+        <v>134068</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>275969</v>
+      </c>
+      <c r="N10" t="n">
+        <v>145045</v>
+      </c>
+      <c r="O10" t="n">
+        <v>135416</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>280461</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bilasipara</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Dhubri</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>95682</v>
+      </c>
+      <c r="F11" t="n">
+        <v>95923</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>191607</v>
+      </c>
+      <c r="I11" t="n">
+        <v>254</v>
+      </c>
+      <c r="J11" t="n">
+        <v>97613</v>
+      </c>
+      <c r="K11" t="n">
+        <v>97783</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>195396</v>
+      </c>
+      <c r="N11" t="n">
+        <v>96378</v>
+      </c>
+      <c r="O11" t="n">
+        <v>95352</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>191730</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mankachar</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>South Salmara</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>149845</v>
+      </c>
+      <c r="F12" t="n">
+        <v>147047</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>296895</v>
+      </c>
+      <c r="I12" t="n">
+        <v>402</v>
+      </c>
+      <c r="J12" t="n">
+        <v>156776</v>
+      </c>
+      <c r="K12" t="n">
+        <v>153240</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>310020</v>
+      </c>
+      <c r="N12" t="n">
+        <v>156903</v>
+      </c>
+      <c r="O12" t="n">
+        <v>153325</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>310232</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Jaleswar</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Goalpara</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>117867</v>
+      </c>
+      <c r="F13" t="n">
+        <v>112166</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>230034</v>
+      </c>
+      <c r="I13" t="n">
+        <v>300</v>
+      </c>
+      <c r="J13" t="n">
+        <v>122913</v>
+      </c>
+      <c r="K13" t="n">
+        <v>116216</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>239134</v>
+      </c>
+      <c r="N13" t="n">
+        <v>124380</v>
+      </c>
+      <c r="O13" t="n">
+        <v>117815</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>242201</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Goalpara West</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Goalpara</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>78827</v>
+      </c>
+      <c r="F14" t="n">
+        <v>79933</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>158765</v>
+      </c>
+      <c r="I14" t="n">
+        <v>205</v>
+      </c>
+      <c r="J14" t="n">
+        <v>80147</v>
+      </c>
+      <c r="K14" t="n">
+        <v>81736</v>
+      </c>
+      <c r="L14" t="n">
+        <v>7</v>
+      </c>
+      <c r="M14" t="n">
+        <v>161890</v>
+      </c>
+      <c r="N14" t="n">
+        <v>79798</v>
+      </c>
+      <c r="O14" t="n">
+        <v>81351</v>
+      </c>
+      <c r="P14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>161156</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Goalpara East</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Goalpara</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>109402</v>
+      </c>
+      <c r="F15" t="n">
+        <v>109654</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>219058</v>
+      </c>
+      <c r="I15" t="n">
+        <v>274</v>
+      </c>
+      <c r="J15" t="n">
+        <v>112465</v>
+      </c>
+      <c r="K15" t="n">
+        <v>112428</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>224896</v>
+      </c>
+      <c r="N15" t="n">
+        <v>114130</v>
+      </c>
+      <c r="O15" t="n">
+        <v>113733</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>227866</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dudhnoi</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Goalpara</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>84774</v>
+      </c>
+      <c r="F16" t="n">
+        <v>90058</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>174833</v>
+      </c>
+      <c r="I16" t="n">
+        <v>231</v>
+      </c>
+      <c r="J16" t="n">
+        <v>85366</v>
+      </c>
+      <c r="K16" t="n">
+        <v>91156</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>176523</v>
+      </c>
+      <c r="N16" t="n">
+        <v>85015</v>
+      </c>
+      <c r="O16" t="n">
+        <v>90576</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>175592</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Abhayapuri</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bongaigaon</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>89099</v>
+      </c>
+      <c r="F17" t="n">
+        <v>89655</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>178756</v>
+      </c>
+      <c r="I17" t="n">
+        <v>236</v>
+      </c>
+      <c r="J17" t="n">
+        <v>90947</v>
+      </c>
+      <c r="K17" t="n">
+        <v>91718</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>182667</v>
+      </c>
+      <c r="N17" t="n">
+        <v>91282</v>
+      </c>
+      <c r="O17" t="n">
+        <v>91093</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>182376</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Srijangram</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bongaigaon</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>112175</v>
+      </c>
+      <c r="F18" t="n">
+        <v>103949</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>216126</v>
+      </c>
+      <c r="I18" t="n">
+        <v>279</v>
+      </c>
+      <c r="J18" t="n">
+        <v>118696</v>
+      </c>
+      <c r="K18" t="n">
+        <v>110502</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>229201</v>
+      </c>
+      <c r="N18" t="n">
+        <v>120702</v>
+      </c>
+      <c r="O18" t="n">
+        <v>112560</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>233266</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bongaigaon</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Bongaigaon</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>83451</v>
+      </c>
+      <c r="F19" t="n">
+        <v>84939</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>168392</v>
+      </c>
+      <c r="I19" t="n">
+        <v>232</v>
+      </c>
+      <c r="J19" t="n">
+        <v>84809</v>
+      </c>
+      <c r="K19" t="n">
+        <v>86448</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>171260</v>
+      </c>
+      <c r="N19" t="n">
+        <v>84773</v>
+      </c>
+      <c r="O19" t="n">
+        <v>86424</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>171200</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sidli Chirang</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Chirang</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>104513</v>
+      </c>
+      <c r="F20" t="n">
+        <v>106123</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>210638</v>
+      </c>
+      <c r="I20" t="n">
+        <v>287</v>
+      </c>
+      <c r="J20" t="n">
+        <v>108456</v>
+      </c>
+      <c r="K20" t="n">
+        <v>110365</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>218825</v>
+      </c>
+      <c r="N20" t="n">
+        <v>108695</v>
+      </c>
+      <c r="O20" t="n">
+        <v>110315</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>219013</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bijni</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Chirang</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>88928</v>
+      </c>
+      <c r="F21" t="n">
+        <v>88679</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>177607</v>
+      </c>
+      <c r="I21" t="n">
+        <v>242</v>
+      </c>
+      <c r="J21" t="n">
+        <v>92390</v>
+      </c>
+      <c r="K21" t="n">
+        <v>92498</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>184888</v>
+      </c>
+      <c r="N21" t="n">
+        <v>91465</v>
+      </c>
+      <c r="O21" t="n">
+        <v>91511</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>182976</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bhawanipur-Sorbhog</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Bajali</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>105557</v>
+      </c>
+      <c r="F22" t="n">
+        <v>103931</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>209493</v>
+      </c>
+      <c r="I22" t="n">
+        <v>270</v>
+      </c>
+      <c r="J22" t="n">
+        <v>107699</v>
+      </c>
+      <c r="K22" t="n">
+        <v>106296</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>213995</v>
+      </c>
+      <c r="N22" t="n">
+        <v>107913</v>
+      </c>
+      <c r="O22" t="n">
+        <v>106894</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>214808</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mandia</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Barpeta</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>134584</v>
+      </c>
+      <c r="F23" t="n">
+        <v>125794</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>260382</v>
+      </c>
+      <c r="I23" t="n">
+        <v>307</v>
+      </c>
+      <c r="J23" t="n">
+        <v>139865</v>
+      </c>
+      <c r="K23" t="n">
+        <v>131339</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>271206</v>
+      </c>
+      <c r="N23" t="n">
+        <v>144961</v>
+      </c>
+      <c r="O23" t="n">
+        <v>136152</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>281115</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Chenga</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Barpeta</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>124858</v>
+      </c>
+      <c r="F24" t="n">
+        <v>114993</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>239856</v>
+      </c>
+      <c r="I24" t="n">
+        <v>284</v>
+      </c>
+      <c r="J24" t="n">
+        <v>128205</v>
+      </c>
+      <c r="K24" t="n">
+        <v>118234</v>
+      </c>
+      <c r="L24" t="n">
+        <v>9</v>
+      </c>
+      <c r="M24" t="n">
+        <v>246448</v>
+      </c>
+      <c r="N24" t="n">
+        <v>134192</v>
+      </c>
+      <c r="O24" t="n">
+        <v>123195</v>
+      </c>
+      <c r="P24" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>257393</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Barpeta</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Barpeta</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>85092</v>
+      </c>
+      <c r="F25" t="n">
+        <v>83618</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>168717</v>
+      </c>
+      <c r="I25" t="n">
+        <v>221</v>
+      </c>
+      <c r="J25" t="n">
+        <v>85881</v>
+      </c>
+      <c r="K25" t="n">
+        <v>84851</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>170735</v>
+      </c>
+      <c r="N25" t="n">
+        <v>86074</v>
+      </c>
+      <c r="O25" t="n">
+        <v>84690</v>
+      </c>
+      <c r="P25" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>170767</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pakabetbari</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Barpeta</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>133768</v>
+      </c>
+      <c r="F26" t="n">
+        <v>124899</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>258672</v>
+      </c>
+      <c r="I26" t="n">
+        <v>309</v>
+      </c>
+      <c r="J26" t="n">
+        <v>138374</v>
+      </c>
+      <c r="K26" t="n">
+        <v>129446</v>
+      </c>
+      <c r="L26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M26" t="n">
+        <v>267823</v>
+      </c>
+      <c r="N26" t="n">
+        <v>142409</v>
+      </c>
+      <c r="O26" t="n">
+        <v>133151</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>275562</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Bajali</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bajali</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>81182</v>
+      </c>
+      <c r="F27" t="n">
+        <v>80249</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>161432</v>
+      </c>
+      <c r="I27" t="n">
+        <v>223</v>
+      </c>
+      <c r="J27" t="n">
+        <v>82592</v>
+      </c>
+      <c r="K27" t="n">
+        <v>82262</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>164854</v>
+      </c>
+      <c r="N27" t="n">
+        <v>82791</v>
+      </c>
+      <c r="O27" t="n">
+        <v>82608</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>165399</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Chamaria</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Kamrup</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>117851</v>
+      </c>
+      <c r="F28" t="n">
+        <v>113720</v>
+      </c>
+      <c r="G28" t="n">
+        <v>7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>231578</v>
+      </c>
+      <c r="I28" t="n">
+        <v>297</v>
+      </c>
+      <c r="J28" t="n">
+        <v>125017</v>
+      </c>
+      <c r="K28" t="n">
+        <v>120368</v>
+      </c>
+      <c r="L28" t="n">
+        <v>5</v>
+      </c>
+      <c r="M28" t="n">
+        <v>245390</v>
+      </c>
+      <c r="N28" t="n">
+        <v>125902</v>
+      </c>
+      <c r="O28" t="n">
+        <v>120629</v>
+      </c>
+      <c r="P28" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>246536</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Boko-Chaygaon</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Kamrup</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>96244</v>
+      </c>
+      <c r="F29" t="n">
+        <v>98022</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>194269</v>
+      </c>
+      <c r="I29" t="n">
+        <v>241</v>
+      </c>
+      <c r="J29" t="n">
+        <v>98794</v>
+      </c>
+      <c r="K29" t="n">
+        <v>101568</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3</v>
+      </c>
+      <c r="M29" t="n">
+        <v>200365</v>
+      </c>
+      <c r="N29" t="n">
+        <v>96872</v>
+      </c>
+      <c r="O29" t="n">
+        <v>98802</v>
+      </c>
+      <c r="P29" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>195677</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Palasbari</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Kamrup</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>104780</v>
+      </c>
+      <c r="F30" t="n">
+        <v>108207</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>212992</v>
+      </c>
+      <c r="I30" t="n">
+        <v>278</v>
+      </c>
+      <c r="J30" t="n">
+        <v>107726</v>
+      </c>
+      <c r="K30" t="n">
+        <v>113273</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>220999</v>
+      </c>
+      <c r="N30" t="n">
+        <v>105242</v>
+      </c>
+      <c r="O30" t="n">
+        <v>110247</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>215489</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Hajo-Sualkuchi</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Kamrup</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>95389</v>
+      </c>
+      <c r="F31" t="n">
+        <v>95188</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>190581</v>
+      </c>
+      <c r="I31" t="n">
+        <v>243</v>
+      </c>
+      <c r="J31" t="n">
+        <v>98917</v>
+      </c>
+      <c r="K31" t="n">
+        <v>99949</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" t="n">
+        <v>198868</v>
+      </c>
+      <c r="N31" t="n">
+        <v>97086</v>
+      </c>
+      <c r="O31" t="n">
+        <v>95676</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>192764</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Rangia</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Kamrup</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>105732</v>
+      </c>
+      <c r="F32" t="n">
+        <v>101850</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>207588</v>
+      </c>
+      <c r="I32" t="n">
+        <v>265</v>
+      </c>
+      <c r="J32" t="n">
+        <v>109341</v>
+      </c>
+      <c r="K32" t="n">
+        <v>107252</v>
+      </c>
+      <c r="L32" t="n">
+        <v>6</v>
+      </c>
+      <c r="M32" t="n">
+        <v>216599</v>
+      </c>
+      <c r="N32" t="n">
+        <v>106752</v>
+      </c>
+      <c r="O32" t="n">
+        <v>102513</v>
+      </c>
+      <c r="P32" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>209271</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kamalpur</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Kamrup</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>91224</v>
+      </c>
+      <c r="F33" t="n">
+        <v>89516</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>180744</v>
+      </c>
+      <c r="I33" t="n">
+        <v>231</v>
+      </c>
+      <c r="J33" t="n">
+        <v>93708</v>
+      </c>
+      <c r="K33" t="n">
+        <v>93816</v>
+      </c>
+      <c r="L33" t="n">
+        <v>5</v>
+      </c>
+      <c r="M33" t="n">
+        <v>187529</v>
+      </c>
+      <c r="N33" t="n">
+        <v>92686</v>
+      </c>
+      <c r="O33" t="n">
+        <v>91603</v>
+      </c>
+      <c r="P33" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>184293</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Dispur</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Kamrup Metro</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>115874</v>
+      </c>
+      <c r="F34" t="n">
+        <v>120224</v>
+      </c>
+      <c r="G34" t="n">
+        <v>14</v>
+      </c>
+      <c r="H34" t="n">
+        <v>236112</v>
+      </c>
+      <c r="I34" t="n">
+        <v>272</v>
+      </c>
+      <c r="J34" t="n">
+        <v>121180</v>
+      </c>
+      <c r="K34" t="n">
+        <v>128552</v>
+      </c>
+      <c r="L34" t="n">
+        <v>14</v>
+      </c>
+      <c r="M34" t="n">
+        <v>249746</v>
+      </c>
+      <c r="N34" t="n">
+        <v>117027</v>
+      </c>
+      <c r="O34" t="n">
+        <v>126137</v>
+      </c>
+      <c r="P34" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>243176</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Dimoria</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Kamrup Metro</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>106624</v>
+      </c>
+      <c r="F35" t="n">
+        <v>110482</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>217111</v>
+      </c>
+      <c r="I35" t="n">
+        <v>262</v>
+      </c>
+      <c r="J35" t="n">
+        <v>107526</v>
+      </c>
+      <c r="K35" t="n">
+        <v>113567</v>
+      </c>
+      <c r="L35" t="n">
+        <v>6</v>
+      </c>
+      <c r="M35" t="n">
+        <v>221099</v>
+      </c>
+      <c r="N35" t="n">
+        <v>105384</v>
+      </c>
+      <c r="O35" t="n">
+        <v>111559</v>
+      </c>
+      <c r="P35" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>216949</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>New Guwahati</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Kamrup Metro</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>94054</v>
+      </c>
+      <c r="F36" t="n">
+        <v>98863</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>192921</v>
+      </c>
+      <c r="I36" t="n">
+        <v>219</v>
+      </c>
+      <c r="J36" t="n">
+        <v>94390</v>
+      </c>
+      <c r="K36" t="n">
+        <v>101621</v>
+      </c>
+      <c r="L36" t="n">
+        <v>5</v>
+      </c>
+      <c r="M36" t="n">
+        <v>196016</v>
+      </c>
+      <c r="N36" t="n">
+        <v>91398</v>
+      </c>
+      <c r="O36" t="n">
+        <v>100045</v>
+      </c>
+      <c r="P36" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>191447</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Guwahati Central</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Kamrup Metro</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>96015</v>
+      </c>
+      <c r="F37" t="n">
+        <v>96158</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" t="n">
+        <v>192179</v>
+      </c>
+      <c r="I37" t="n">
+        <v>218</v>
+      </c>
+      <c r="J37" t="n">
+        <v>97885</v>
+      </c>
+      <c r="K37" t="n">
+        <v>100202</v>
+      </c>
+      <c r="L37" t="n">
+        <v>4</v>
+      </c>
+      <c r="M37" t="n">
+        <v>198091</v>
+      </c>
+      <c r="N37" t="n">
+        <v>93967</v>
+      </c>
+      <c r="O37" t="n">
+        <v>97788</v>
+      </c>
+      <c r="P37" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>191758</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Jalukbari</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Kamrup Metro</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>97677</v>
+      </c>
+      <c r="F38" t="n">
+        <v>104703</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>202385</v>
+      </c>
+      <c r="I38" t="n">
+        <v>247</v>
+      </c>
+      <c r="J38" t="n">
+        <v>100407</v>
+      </c>
+      <c r="K38" t="n">
+        <v>110209</v>
+      </c>
+      <c r="L38" t="n">
+        <v>8</v>
+      </c>
+      <c r="M38" t="n">
+        <v>210624</v>
+      </c>
+      <c r="N38" t="n">
+        <v>97653</v>
+      </c>
+      <c r="O38" t="n">
+        <v>108654</v>
+      </c>
+      <c r="P38" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>206314</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Barkhetri</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Nalbari</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>112039</v>
+      </c>
+      <c r="F39" t="n">
+        <v>104988</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>217028</v>
+      </c>
+      <c r="I39" t="n">
+        <v>292</v>
+      </c>
+      <c r="J39" t="n">
+        <v>116394</v>
+      </c>
+      <c r="K39" t="n">
+        <v>110029</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>226424</v>
+      </c>
+      <c r="N39" t="n">
+        <v>113184</v>
+      </c>
+      <c r="O39" t="n">
+        <v>106487</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>219672</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Nalbari</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Nalbari</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>99471</v>
+      </c>
+      <c r="F40" t="n">
+        <v>95630</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>195101</v>
+      </c>
+      <c r="I40" t="n">
+        <v>269</v>
+      </c>
+      <c r="J40" t="n">
+        <v>101753</v>
+      </c>
+      <c r="K40" t="n">
+        <v>99291</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>201044</v>
+      </c>
+      <c r="N40" t="n">
+        <v>101985</v>
+      </c>
+      <c r="O40" t="n">
+        <v>98293</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>200278</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Tihu</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Nalbari</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103522</v>
+      </c>
+      <c r="F41" t="n">
+        <v>98179</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>201701</v>
+      </c>
+      <c r="I41" t="n">
+        <v>264</v>
+      </c>
+      <c r="J41" t="n">
+        <v>105677</v>
+      </c>
+      <c r="K41" t="n">
+        <v>102085</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>207763</v>
+      </c>
+      <c r="N41" t="n">
+        <v>104715</v>
+      </c>
+      <c r="O41" t="n">
+        <v>99725</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>204441</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Manas</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Baksa</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>101250</v>
+      </c>
+      <c r="F42" t="n">
+        <v>99151</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>200403</v>
+      </c>
+      <c r="I42" t="n">
+        <v>258</v>
+      </c>
+      <c r="J42" t="n">
+        <v>104013</v>
+      </c>
+      <c r="K42" t="n">
+        <v>102586</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>206599</v>
+      </c>
+      <c r="N42" t="n">
+        <v>103114</v>
+      </c>
+      <c r="O42" t="n">
+        <v>101527</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>204641</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Baksa</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Baksa</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>96491</v>
+      </c>
+      <c r="F43" t="n">
+        <v>97958</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>194451</v>
+      </c>
+      <c r="I43" t="n">
+        <v>244</v>
+      </c>
+      <c r="J43" t="n">
+        <v>99872</v>
+      </c>
+      <c r="K43" t="n">
+        <v>102277</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>202150</v>
+      </c>
+      <c r="N43" t="n">
+        <v>97864</v>
+      </c>
+      <c r="O43" t="n">
+        <v>99822</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>197687</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Tamulpur</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Tamulpur</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>106954</v>
+      </c>
+      <c r="F44" t="n">
+        <v>105303</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>212257</v>
+      </c>
+      <c r="I44" t="n">
+        <v>250</v>
+      </c>
+      <c r="J44" t="n">
+        <v>108362</v>
+      </c>
+      <c r="K44" t="n">
+        <v>107935</v>
+      </c>
+      <c r="L44" t="n">
+        <v>2</v>
+      </c>
+      <c r="M44" t="n">
+        <v>216299</v>
+      </c>
+      <c r="N44" t="n">
+        <v>107458</v>
+      </c>
+      <c r="O44" t="n">
+        <v>106387</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>213846</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Goreswar</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Tamulpur</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100306</v>
+      </c>
+      <c r="F45" t="n">
+        <v>99100</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>199407</v>
+      </c>
+      <c r="I45" t="n">
+        <v>232</v>
+      </c>
+      <c r="J45" t="n">
+        <v>104491</v>
+      </c>
+      <c r="K45" t="n">
+        <v>104919</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
+        <v>209411</v>
+      </c>
+      <c r="N45" t="n">
+        <v>102555</v>
+      </c>
+      <c r="O45" t="n">
+        <v>102612</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>205167</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Bhergaon</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Udalguri</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>79040</v>
+      </c>
+      <c r="F46" t="n">
+        <v>81287</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>160329</v>
+      </c>
+      <c r="I46" t="n">
+        <v>203</v>
+      </c>
+      <c r="J46" t="n">
+        <v>80857</v>
+      </c>
+      <c r="K46" t="n">
+        <v>83785</v>
+      </c>
+      <c r="L46" t="n">
+        <v>3</v>
+      </c>
+      <c r="M46" t="n">
+        <v>164645</v>
+      </c>
+      <c r="N46" t="n">
+        <v>79056</v>
+      </c>
+      <c r="O46" t="n">
+        <v>81128</v>
+      </c>
+      <c r="P46" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>160187</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Udalguri</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Udalguri</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>83703</v>
+      </c>
+      <c r="F47" t="n">
+        <v>85528</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>169232</v>
+      </c>
+      <c r="I47" t="n">
+        <v>210</v>
+      </c>
+      <c r="J47" t="n">
+        <v>86292</v>
+      </c>
+      <c r="K47" t="n">
+        <v>88655</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>174948</v>
+      </c>
+      <c r="N47" t="n">
+        <v>83741</v>
+      </c>
+      <c r="O47" t="n">
+        <v>85464</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>169206</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Mazbat</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Udalguri</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>90966</v>
+      </c>
+      <c r="F48" t="n">
+        <v>91274</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>182241</v>
+      </c>
+      <c r="I48" t="n">
+        <v>213</v>
+      </c>
+      <c r="J48" t="n">
+        <v>93831</v>
+      </c>
+      <c r="K48" t="n">
+        <v>95310</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>189143</v>
+      </c>
+      <c r="N48" t="n">
+        <v>92417</v>
+      </c>
+      <c r="O48" t="n">
+        <v>93096</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>185514</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Tangla</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Udalguri</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>87686</v>
+      </c>
+      <c r="F49" t="n">
+        <v>89718</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>177404</v>
+      </c>
+      <c r="I49" t="n">
+        <v>239</v>
+      </c>
+      <c r="J49" t="n">
+        <v>91469</v>
+      </c>
+      <c r="K49" t="n">
+        <v>94393</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>185862</v>
+      </c>
+      <c r="N49" t="n">
+        <v>89232</v>
+      </c>
+      <c r="O49" t="n">
+        <v>90709</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>179941</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sipajhar</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Darrang</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>104118</v>
+      </c>
+      <c r="F50" t="n">
+        <v>100626</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>204749</v>
+      </c>
+      <c r="I50" t="n">
+        <v>290</v>
+      </c>
+      <c r="J50" t="n">
+        <v>106611</v>
+      </c>
+      <c r="K50" t="n">
+        <v>104683</v>
+      </c>
+      <c r="L50" t="n">
+        <v>5</v>
+      </c>
+      <c r="M50" t="n">
+        <v>211299</v>
+      </c>
+      <c r="N50" t="n">
+        <v>103050</v>
+      </c>
+      <c r="O50" t="n">
+        <v>98829</v>
+      </c>
+      <c r="P50" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>201883</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Mangaldai</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Darrang</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>98241</v>
+      </c>
+      <c r="F51" t="n">
+        <v>97120</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>195363</v>
+      </c>
+      <c r="I51" t="n">
+        <v>251</v>
+      </c>
+      <c r="J51" t="n">
+        <v>104057</v>
+      </c>
+      <c r="K51" t="n">
+        <v>103631</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3</v>
+      </c>
+      <c r="M51" t="n">
+        <v>207691</v>
+      </c>
+      <c r="N51" t="n">
+        <v>101161</v>
+      </c>
+      <c r="O51" t="n">
+        <v>99209</v>
+      </c>
+      <c r="P51" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>200373</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Dalgaon</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Darrang</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>151324</v>
+      </c>
+      <c r="F52" t="n">
+        <v>146514</v>
+      </c>
+      <c r="G52" t="n">
+        <v>8</v>
+      </c>
+      <c r="H52" t="n">
+        <v>297846</v>
+      </c>
+      <c r="I52" t="n">
+        <v>366</v>
+      </c>
+      <c r="J52" t="n">
+        <v>160624</v>
+      </c>
+      <c r="K52" t="n">
+        <v>157692</v>
+      </c>
+      <c r="L52" t="n">
+        <v>10</v>
+      </c>
+      <c r="M52" t="n">
+        <v>318326</v>
+      </c>
+      <c r="N52" t="n">
+        <v>159641</v>
+      </c>
+      <c r="O52" t="n">
+        <v>155633</v>
+      </c>
+      <c r="P52" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>315284</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Jagiroad</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Morigaon</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>118705</v>
+      </c>
+      <c r="F53" t="n">
+        <v>118097</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>236802</v>
+      </c>
+      <c r="I53" t="n">
+        <v>335</v>
+      </c>
+      <c r="J53" t="n">
+        <v>124729</v>
+      </c>
+      <c r="K53" t="n">
+        <v>125411</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>250142</v>
+      </c>
+      <c r="N53" t="n">
+        <v>125521</v>
+      </c>
+      <c r="O53" t="n">
+        <v>126232</v>
+      </c>
+      <c r="P53" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>251755</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Laharighat</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Morigaon</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>145004</v>
+      </c>
+      <c r="F54" t="n">
+        <v>136790</v>
+      </c>
+      <c r="G54" t="n">
+        <v>9</v>
+      </c>
+      <c r="H54" t="n">
+        <v>281803</v>
+      </c>
+      <c r="I54" t="n">
+        <v>355</v>
+      </c>
+      <c r="J54" t="n">
+        <v>155191</v>
+      </c>
+      <c r="K54" t="n">
+        <v>146384</v>
+      </c>
+      <c r="L54" t="n">
+        <v>6</v>
+      </c>
+      <c r="M54" t="n">
+        <v>301581</v>
+      </c>
+      <c r="N54" t="n">
+        <v>159335</v>
+      </c>
+      <c r="O54" t="n">
+        <v>149797</v>
+      </c>
+      <c r="P54" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>309141</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Morigaon</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Morigaon</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100331</v>
+      </c>
+      <c r="F55" t="n">
+        <v>100989</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" t="n">
+        <v>201322</v>
+      </c>
+      <c r="I55" t="n">
+        <v>278</v>
+      </c>
+      <c r="J55" t="n">
+        <v>103819</v>
+      </c>
+      <c r="K55" t="n">
+        <v>106147</v>
+      </c>
+      <c r="L55" t="n">
+        <v>2</v>
+      </c>
+      <c r="M55" t="n">
+        <v>209968</v>
+      </c>
+      <c r="N55" t="n">
+        <v>102191</v>
+      </c>
+      <c r="O55" t="n">
+        <v>103825</v>
+      </c>
+      <c r="P55" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>206019</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Dhing</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Nagaon</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>113240</v>
+      </c>
+      <c r="F56" t="n">
+        <v>107225</v>
+      </c>
+      <c r="G56" t="n">
+        <v>12</v>
+      </c>
+      <c r="H56" t="n">
+        <v>220477</v>
+      </c>
+      <c r="I56" t="n">
+        <v>266</v>
+      </c>
+      <c r="J56" t="n">
+        <v>118947</v>
+      </c>
+      <c r="K56" t="n">
+        <v>113221</v>
+      </c>
+      <c r="L56" t="n">
+        <v>9</v>
+      </c>
+      <c r="M56" t="n">
+        <v>232177</v>
+      </c>
+      <c r="N56" t="n">
+        <v>121089</v>
+      </c>
+      <c r="O56" t="n">
+        <v>114384</v>
+      </c>
+      <c r="P56" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>235481</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Rupahihat</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Nagaon</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>110155</v>
+      </c>
+      <c r="F57" t="n">
+        <v>105455</v>
+      </c>
+      <c r="G57" t="n">
+        <v>17</v>
+      </c>
+      <c r="H57" t="n">
+        <v>215627</v>
+      </c>
+      <c r="I57" t="n">
+        <v>262</v>
+      </c>
+      <c r="J57" t="n">
+        <v>115687</v>
+      </c>
+      <c r="K57" t="n">
+        <v>110172</v>
+      </c>
+      <c r="L57" t="n">
+        <v>7</v>
+      </c>
+      <c r="M57" t="n">
+        <v>225866</v>
+      </c>
+      <c r="N57" t="n">
+        <v>118661</v>
+      </c>
+      <c r="O57" t="n">
+        <v>112918</v>
+      </c>
+      <c r="P57" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>231584</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Kaliabor</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Nagaon</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>91477</v>
+      </c>
+      <c r="F58" t="n">
+        <v>92507</v>
+      </c>
+      <c r="G58" t="n">
+        <v>8</v>
+      </c>
+      <c r="H58" t="n">
+        <v>183992</v>
+      </c>
+      <c r="I58" t="n">
+        <v>245</v>
+      </c>
+      <c r="J58" t="n">
+        <v>93466</v>
+      </c>
+      <c r="K58" t="n">
+        <v>94948</v>
+      </c>
+      <c r="L58" t="n">
+        <v>6</v>
+      </c>
+      <c r="M58" t="n">
+        <v>188420</v>
+      </c>
+      <c r="N58" t="n">
+        <v>93970</v>
+      </c>
+      <c r="O58" t="n">
+        <v>95006</v>
+      </c>
+      <c r="P58" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>188982</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Samaguri</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Nagaon</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>106909</v>
+      </c>
+      <c r="F59" t="n">
+        <v>105036</v>
+      </c>
+      <c r="G59" t="n">
+        <v>11</v>
+      </c>
+      <c r="H59" t="n">
+        <v>211956</v>
+      </c>
+      <c r="I59" t="n">
+        <v>259</v>
+      </c>
+      <c r="J59" t="n">
+        <v>111934</v>
+      </c>
+      <c r="K59" t="n">
+        <v>110141</v>
+      </c>
+      <c r="L59" t="n">
+        <v>7</v>
+      </c>
+      <c r="M59" t="n">
+        <v>222082</v>
+      </c>
+      <c r="N59" t="n">
+        <v>113785</v>
+      </c>
+      <c r="O59" t="n">
+        <v>111035</v>
+      </c>
+      <c r="P59" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>224826</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Barhampur</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Nagaon</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>112948</v>
+      </c>
+      <c r="F60" t="n">
+        <v>114644</v>
+      </c>
+      <c r="G60" t="n">
+        <v>7</v>
+      </c>
+      <c r="H60" t="n">
+        <v>227599</v>
+      </c>
+      <c r="I60" t="n">
+        <v>284</v>
+      </c>
+      <c r="J60" t="n">
+        <v>114802</v>
+      </c>
+      <c r="K60" t="n">
+        <v>115743</v>
+      </c>
+      <c r="L60" t="n">
+        <v>6</v>
+      </c>
+      <c r="M60" t="n">
+        <v>230551</v>
+      </c>
+      <c r="N60" t="n">
+        <v>114711</v>
+      </c>
+      <c r="O60" t="n">
+        <v>115751</v>
+      </c>
+      <c r="P60" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>230471</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Nagaon-Batadraba</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Nagaon</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>96921</v>
+      </c>
+      <c r="F61" t="n">
+        <v>102752</v>
+      </c>
+      <c r="G61" t="n">
+        <v>15</v>
+      </c>
+      <c r="H61" t="n">
+        <v>199688</v>
+      </c>
+      <c r="I61" t="n">
+        <v>250</v>
+      </c>
+      <c r="J61" t="n">
+        <v>97408</v>
+      </c>
+      <c r="K61" t="n">
+        <v>104536</v>
+      </c>
+      <c r="L61" t="n">
+        <v>11</v>
+      </c>
+      <c r="M61" t="n">
+        <v>201955</v>
+      </c>
+      <c r="N61" t="n">
+        <v>95348</v>
+      </c>
+      <c r="O61" t="n">
+        <v>101930</v>
+      </c>
+      <c r="P61" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>197284</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Raha</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Nagaon</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>117595</v>
+      </c>
+      <c r="F62" t="n">
+        <v>119186</v>
+      </c>
+      <c r="G62" t="n">
+        <v>16</v>
+      </c>
+      <c r="H62" t="n">
+        <v>236797</v>
+      </c>
+      <c r="I62" t="n">
+        <v>302</v>
+      </c>
+      <c r="J62" t="n">
+        <v>120297</v>
+      </c>
+      <c r="K62" t="n">
+        <v>122648</v>
+      </c>
+      <c r="L62" t="n">
+        <v>15</v>
+      </c>
+      <c r="M62" t="n">
+        <v>242960</v>
+      </c>
+      <c r="N62" t="n">
+        <v>120644</v>
+      </c>
+      <c r="O62" t="n">
+        <v>122246</v>
+      </c>
+      <c r="P62" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>242902</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Binnakandi</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Hojai</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>129929</v>
+      </c>
+      <c r="F63" t="n">
+        <v>123555</v>
+      </c>
+      <c r="G63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H63" t="n">
+        <v>253490</v>
+      </c>
+      <c r="I63" t="n">
+        <v>345</v>
+      </c>
+      <c r="J63" t="n">
+        <v>136089</v>
+      </c>
+      <c r="K63" t="n">
+        <v>129827</v>
+      </c>
+      <c r="L63" t="n">
+        <v>4</v>
+      </c>
+      <c r="M63" t="n">
+        <v>265920</v>
+      </c>
+      <c r="N63" t="n">
+        <v>138002</v>
+      </c>
+      <c r="O63" t="n">
+        <v>130438</v>
+      </c>
+      <c r="P63" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>268443</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Hojai</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Hojai</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>123895</v>
+      </c>
+      <c r="F64" t="n">
+        <v>119668</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>243564</v>
+      </c>
+      <c r="I64" t="n">
+        <v>316</v>
+      </c>
+      <c r="J64" t="n">
+        <v>128526</v>
+      </c>
+      <c r="K64" t="n">
+        <v>124818</v>
+      </c>
+      <c r="L64" t="n">
+        <v>2</v>
+      </c>
+      <c r="M64" t="n">
+        <v>253346</v>
+      </c>
+      <c r="N64" t="n">
+        <v>127766</v>
+      </c>
+      <c r="O64" t="n">
+        <v>122643</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>250410</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Lumding</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Hojai</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>120730</v>
+      </c>
+      <c r="F65" t="n">
+        <v>117943</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2</v>
+      </c>
+      <c r="H65" t="n">
+        <v>238675</v>
+      </c>
+      <c r="I65" t="n">
+        <v>323</v>
+      </c>
+      <c r="J65" t="n">
+        <v>124372</v>
+      </c>
+      <c r="K65" t="n">
+        <v>121645</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" t="n">
+        <v>246018</v>
+      </c>
+      <c r="N65" t="n">
+        <v>123858</v>
+      </c>
+      <c r="O65" t="n">
+        <v>119710</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>243569</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Dhekiajuli</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Sonitpur</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>111467</v>
+      </c>
+      <c r="F66" t="n">
+        <v>109630</v>
+      </c>
+      <c r="G66" t="n">
+        <v>4</v>
+      </c>
+      <c r="H66" t="n">
+        <v>221101</v>
+      </c>
+      <c r="I66" t="n">
+        <v>285</v>
+      </c>
+      <c r="J66" t="n">
+        <v>114503</v>
+      </c>
+      <c r="K66" t="n">
+        <v>113994</v>
+      </c>
+      <c r="L66" t="n">
+        <v>4</v>
+      </c>
+      <c r="M66" t="n">
+        <v>228501</v>
+      </c>
+      <c r="N66" t="n">
+        <v>112538</v>
+      </c>
+      <c r="O66" t="n">
+        <v>111366</v>
+      </c>
+      <c r="P66" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>223906</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Barchalla</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sonitpur</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>95029</v>
+      </c>
+      <c r="F67" t="n">
+        <v>94632</v>
+      </c>
+      <c r="G67" t="n">
+        <v>6</v>
+      </c>
+      <c r="H67" t="n">
+        <v>189667</v>
+      </c>
+      <c r="I67" t="n">
+        <v>251</v>
+      </c>
+      <c r="J67" t="n">
+        <v>97395</v>
+      </c>
+      <c r="K67" t="n">
+        <v>98342</v>
+      </c>
+      <c r="L67" t="n">
+        <v>7</v>
+      </c>
+      <c r="M67" t="n">
+        <v>195744</v>
+      </c>
+      <c r="N67" t="n">
+        <v>95103</v>
+      </c>
+      <c r="O67" t="n">
+        <v>94535</v>
+      </c>
+      <c r="P67" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>189645</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Tezpur</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Sonitpur</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>85257</v>
+      </c>
+      <c r="F68" t="n">
+        <v>89631</v>
+      </c>
+      <c r="G68" t="n">
+        <v>4</v>
+      </c>
+      <c r="H68" t="n">
+        <v>174892</v>
+      </c>
+      <c r="I68" t="n">
+        <v>225</v>
+      </c>
+      <c r="J68" t="n">
+        <v>87550</v>
+      </c>
+      <c r="K68" t="n">
+        <v>93332</v>
+      </c>
+      <c r="L68" t="n">
+        <v>3</v>
+      </c>
+      <c r="M68" t="n">
+        <v>180885</v>
+      </c>
+      <c r="N68" t="n">
+        <v>84893</v>
+      </c>
+      <c r="O68" t="n">
+        <v>90667</v>
+      </c>
+      <c r="P68" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>175563</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Rangapara</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Sonitpur</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>81766</v>
+      </c>
+      <c r="F69" t="n">
+        <v>85000</v>
+      </c>
+      <c r="G69" t="n">
+        <v>6</v>
+      </c>
+      <c r="H69" t="n">
+        <v>166772</v>
+      </c>
+      <c r="I69" t="n">
+        <v>214</v>
+      </c>
+      <c r="J69" t="n">
+        <v>83604</v>
+      </c>
+      <c r="K69" t="n">
+        <v>88356</v>
+      </c>
+      <c r="L69" t="n">
+        <v>5</v>
+      </c>
+      <c r="M69" t="n">
+        <v>171965</v>
+      </c>
+      <c r="N69" t="n">
+        <v>82105</v>
+      </c>
+      <c r="O69" t="n">
+        <v>86918</v>
+      </c>
+      <c r="P69" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>169029</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Naduar</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Sonitpur</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>99518</v>
+      </c>
+      <c r="F70" t="n">
+        <v>99331</v>
+      </c>
+      <c r="G70" t="n">
+        <v>4</v>
+      </c>
+      <c r="H70" t="n">
+        <v>198853</v>
+      </c>
+      <c r="I70" t="n">
+        <v>256</v>
+      </c>
+      <c r="J70" t="n">
+        <v>102103</v>
+      </c>
+      <c r="K70" t="n">
+        <v>102622</v>
+      </c>
+      <c r="L70" t="n">
+        <v>3</v>
+      </c>
+      <c r="M70" t="n">
+        <v>204728</v>
+      </c>
+      <c r="N70" t="n">
+        <v>100670</v>
+      </c>
+      <c r="O70" t="n">
+        <v>100822</v>
+      </c>
+      <c r="P70" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>201494</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Biswanath</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Biswanath</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>92586</v>
+      </c>
+      <c r="F71" t="n">
+        <v>93656</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3</v>
+      </c>
+      <c r="H71" t="n">
+        <v>186245</v>
+      </c>
+      <c r="I71" t="n">
+        <v>238</v>
+      </c>
+      <c r="J71" t="n">
+        <v>94129</v>
+      </c>
+      <c r="K71" t="n">
+        <v>96497</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" t="n">
+        <v>190627</v>
+      </c>
+      <c r="N71" t="n">
+        <v>93206</v>
+      </c>
+      <c r="O71" t="n">
+        <v>94615</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>187821</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Behali</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Biswanath</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>76964</v>
+      </c>
+      <c r="F72" t="n">
+        <v>77072</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>154037</v>
+      </c>
+      <c r="I72" t="n">
+        <v>197</v>
+      </c>
+      <c r="J72" t="n">
+        <v>78117</v>
+      </c>
+      <c r="K72" t="n">
+        <v>79950</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" t="n">
+        <v>158068</v>
+      </c>
+      <c r="N72" t="n">
+        <v>76543</v>
+      </c>
+      <c r="O72" t="n">
+        <v>77655</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>154199</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Gohpur</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Biswanath</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>86009</v>
+      </c>
+      <c r="F73" t="n">
+        <v>84318</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>170327</v>
+      </c>
+      <c r="I73" t="n">
+        <v>218</v>
+      </c>
+      <c r="J73" t="n">
+        <v>86850</v>
+      </c>
+      <c r="K73" t="n">
+        <v>86629</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>173479</v>
+      </c>
+      <c r="N73" t="n">
+        <v>86609</v>
+      </c>
+      <c r="O73" t="n">
+        <v>84970</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>171579</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Bihpuria</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Lakhimpur</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>81516</v>
+      </c>
+      <c r="F74" t="n">
+        <v>81952</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2</v>
+      </c>
+      <c r="H74" t="n">
+        <v>163470</v>
+      </c>
+      <c r="I74" t="n">
+        <v>206</v>
+      </c>
+      <c r="J74" t="n">
+        <v>83555</v>
+      </c>
+      <c r="K74" t="n">
+        <v>85492</v>
+      </c>
+      <c r="L74" t="n">
+        <v>2</v>
+      </c>
+      <c r="M74" t="n">
+        <v>169049</v>
+      </c>
+      <c r="N74" t="n">
+        <v>82991</v>
+      </c>
+      <c r="O74" t="n">
+        <v>83649</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>166640</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Rongonadi</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Lakhimpur</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>84621</v>
+      </c>
+      <c r="F75" t="n">
+        <v>84820</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="n">
+        <v>169442</v>
+      </c>
+      <c r="I75" t="n">
+        <v>222</v>
+      </c>
+      <c r="J75" t="n">
+        <v>89741</v>
+      </c>
+      <c r="K75" t="n">
+        <v>90668</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3</v>
+      </c>
+      <c r="M75" t="n">
+        <v>180412</v>
+      </c>
+      <c r="N75" t="n">
+        <v>88677</v>
+      </c>
+      <c r="O75" t="n">
+        <v>88644</v>
+      </c>
+      <c r="P75" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>177324</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Nowboicha</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Lakhimpur</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>84958</v>
+      </c>
+      <c r="F76" t="n">
+        <v>83510</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>168469</v>
+      </c>
+      <c r="I76" t="n">
+        <v>215</v>
+      </c>
+      <c r="J76" t="n">
+        <v>88368</v>
+      </c>
+      <c r="K76" t="n">
+        <v>87442</v>
+      </c>
+      <c r="L76" t="n">
+        <v>3</v>
+      </c>
+      <c r="M76" t="n">
+        <v>175813</v>
+      </c>
+      <c r="N76" t="n">
+        <v>87671</v>
+      </c>
+      <c r="O76" t="n">
+        <v>85138</v>
+      </c>
+      <c r="P76" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>172811</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Lakhimpur</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Lakhimpur</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>82041</v>
+      </c>
+      <c r="F77" t="n">
+        <v>83949</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>165991</v>
+      </c>
+      <c r="I77" t="n">
+        <v>210</v>
+      </c>
+      <c r="J77" t="n">
+        <v>85283</v>
+      </c>
+      <c r="K77" t="n">
+        <v>88078</v>
+      </c>
+      <c r="L77" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" t="n">
+        <v>173362</v>
+      </c>
+      <c r="N77" t="n">
+        <v>81120</v>
+      </c>
+      <c r="O77" t="n">
+        <v>82402</v>
+      </c>
+      <c r="P77" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>163526</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Dhakuakhana</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Lakhimpur</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>80795</v>
+      </c>
+      <c r="F78" t="n">
+        <v>79689</v>
+      </c>
+      <c r="G78" t="n">
+        <v>3</v>
+      </c>
+      <c r="H78" t="n">
+        <v>160487</v>
+      </c>
+      <c r="I78" t="n">
+        <v>226</v>
+      </c>
+      <c r="J78" t="n">
+        <v>82772</v>
+      </c>
+      <c r="K78" t="n">
+        <v>82594</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>165366</v>
+      </c>
+      <c r="N78" t="n">
+        <v>81840</v>
+      </c>
+      <c r="O78" t="n">
+        <v>80863</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>162703</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Dhemaji</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Dhemaji</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>85389</v>
+      </c>
+      <c r="F79" t="n">
+        <v>85730</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>171119</v>
+      </c>
+      <c r="I79" t="n">
+        <v>226</v>
+      </c>
+      <c r="J79" t="n">
+        <v>88754</v>
+      </c>
+      <c r="K79" t="n">
+        <v>90076</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>178830</v>
+      </c>
+      <c r="N79" t="n">
+        <v>88580</v>
+      </c>
+      <c r="O79" t="n">
+        <v>89739</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>178319</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Sissiborgaon</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Dhemaji</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>88484</v>
+      </c>
+      <c r="F80" t="n">
+        <v>86138</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>174623</v>
+      </c>
+      <c r="I80" t="n">
+        <v>230</v>
+      </c>
+      <c r="J80" t="n">
+        <v>91228</v>
+      </c>
+      <c r="K80" t="n">
+        <v>90087</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>181315</v>
+      </c>
+      <c r="N80" t="n">
+        <v>91381</v>
+      </c>
+      <c r="O80" t="n">
+        <v>90102</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>181483</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Jonai</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Dhemaji</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>106695</v>
+      </c>
+      <c r="F81" t="n">
+        <v>107180</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>213876</v>
+      </c>
+      <c r="I81" t="n">
+        <v>282</v>
+      </c>
+      <c r="J81" t="n">
+        <v>111398</v>
+      </c>
+      <c r="K81" t="n">
+        <v>112333</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>223731</v>
+      </c>
+      <c r="N81" t="n">
+        <v>110932</v>
+      </c>
+      <c r="O81" t="n">
+        <v>111114</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>222046</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Sadiya</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Tinsukia</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>99993</v>
+      </c>
+      <c r="F82" t="n">
+        <v>99170</v>
+      </c>
+      <c r="G82" t="n">
+        <v>5</v>
+      </c>
+      <c r="H82" t="n">
+        <v>199168</v>
+      </c>
+      <c r="I82" t="n">
+        <v>268</v>
+      </c>
+      <c r="J82" t="n">
+        <v>102094</v>
+      </c>
+      <c r="K82" t="n">
+        <v>101847</v>
+      </c>
+      <c r="L82" t="n">
+        <v>4</v>
+      </c>
+      <c r="M82" t="n">
+        <v>203945</v>
+      </c>
+      <c r="N82" t="n">
+        <v>101122</v>
+      </c>
+      <c r="O82" t="n">
+        <v>100386</v>
+      </c>
+      <c r="P82" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>201512</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Doom Dooma</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Tinsukia</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>68818</v>
+      </c>
+      <c r="F83" t="n">
+        <v>74241</v>
+      </c>
+      <c r="G83" t="n">
+        <v>7</v>
+      </c>
+      <c r="H83" t="n">
+        <v>143066</v>
+      </c>
+      <c r="I83" t="n">
+        <v>181</v>
+      </c>
+      <c r="J83" t="n">
+        <v>70244</v>
+      </c>
+      <c r="K83" t="n">
+        <v>76258</v>
+      </c>
+      <c r="L83" t="n">
+        <v>7</v>
+      </c>
+      <c r="M83" t="n">
+        <v>146509</v>
+      </c>
+      <c r="N83" t="n">
+        <v>69867</v>
+      </c>
+      <c r="O83" t="n">
+        <v>78119</v>
+      </c>
+      <c r="P83" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>147990</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Margherita</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Tinsukia</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>82865</v>
+      </c>
+      <c r="F84" t="n">
+        <v>84367</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>167232</v>
+      </c>
+      <c r="I84" t="n">
+        <v>222</v>
+      </c>
+      <c r="J84" t="n">
+        <v>86416</v>
+      </c>
+      <c r="K84" t="n">
+        <v>88554</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>174970</v>
+      </c>
+      <c r="N84" t="n">
+        <v>86401</v>
+      </c>
+      <c r="O84" t="n">
+        <v>89708</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>176109</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Digboi</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Tinsukia</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>69806</v>
+      </c>
+      <c r="F85" t="n">
+        <v>72802</v>
+      </c>
+      <c r="G85" t="n">
+        <v>3</v>
+      </c>
+      <c r="H85" t="n">
+        <v>142611</v>
+      </c>
+      <c r="I85" t="n">
+        <v>189</v>
+      </c>
+      <c r="J85" t="n">
+        <v>71536</v>
+      </c>
+      <c r="K85" t="n">
+        <v>75377</v>
+      </c>
+      <c r="L85" t="n">
+        <v>4</v>
+      </c>
+      <c r="M85" t="n">
+        <v>146917</v>
+      </c>
+      <c r="N85" t="n">
+        <v>70873</v>
+      </c>
+      <c r="O85" t="n">
+        <v>76223</v>
+      </c>
+      <c r="P85" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>147098</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Makum</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Tinsukia</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>75117</v>
+      </c>
+      <c r="F86" t="n">
+        <v>81037</v>
+      </c>
+      <c r="G86" t="n">
+        <v>5</v>
+      </c>
+      <c r="H86" t="n">
+        <v>156159</v>
+      </c>
+      <c r="I86" t="n">
+        <v>204</v>
+      </c>
+      <c r="J86" t="n">
+        <v>76571</v>
+      </c>
+      <c r="K86" t="n">
+        <v>82942</v>
+      </c>
+      <c r="L86" t="n">
+        <v>5</v>
+      </c>
+      <c r="M86" t="n">
+        <v>159518</v>
+      </c>
+      <c r="N86" t="n">
+        <v>75457</v>
+      </c>
+      <c r="O86" t="n">
+        <v>82967</v>
+      </c>
+      <c r="P86" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>158430</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Tinsukia</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Tinsukia</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>84998</v>
+      </c>
+      <c r="F87" t="n">
+        <v>87542</v>
+      </c>
+      <c r="G87" t="n">
+        <v>16</v>
+      </c>
+      <c r="H87" t="n">
+        <v>172556</v>
+      </c>
+      <c r="I87" t="n">
+        <v>216</v>
+      </c>
+      <c r="J87" t="n">
+        <v>86516</v>
+      </c>
+      <c r="K87" t="n">
+        <v>89765</v>
+      </c>
+      <c r="L87" t="n">
+        <v>18</v>
+      </c>
+      <c r="M87" t="n">
+        <v>176299</v>
+      </c>
+      <c r="N87" t="n">
+        <v>84022</v>
+      </c>
+      <c r="O87" t="n">
+        <v>88311</v>
+      </c>
+      <c r="P87" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>172351</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Chabua-Lahowal</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Dibrugarh</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>84626</v>
+      </c>
+      <c r="F88" t="n">
+        <v>89251</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>173877</v>
+      </c>
+      <c r="I88" t="n">
+        <v>230</v>
+      </c>
+      <c r="J88" t="n">
+        <v>86328</v>
+      </c>
+      <c r="K88" t="n">
+        <v>92764</v>
+      </c>
+      <c r="L88" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" t="n">
+        <v>179093</v>
+      </c>
+      <c r="N88" t="n">
+        <v>85256</v>
+      </c>
+      <c r="O88" t="n">
+        <v>91981</v>
+      </c>
+      <c r="P88" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>177238</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Dibrugarh</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Dibrugarh</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>91953</v>
+      </c>
+      <c r="F89" t="n">
+        <v>98542</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>190496</v>
+      </c>
+      <c r="I89" t="n">
+        <v>238</v>
+      </c>
+      <c r="J89" t="n">
+        <v>94172</v>
+      </c>
+      <c r="K89" t="n">
+        <v>102501</v>
+      </c>
+      <c r="L89" t="n">
+        <v>2</v>
+      </c>
+      <c r="M89" t="n">
+        <v>196675</v>
+      </c>
+      <c r="N89" t="n">
+        <v>93685</v>
+      </c>
+      <c r="O89" t="n">
+        <v>103467</v>
+      </c>
+      <c r="P89" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>197154</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Khowang</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Dibrugarh</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>75203</v>
+      </c>
+      <c r="F90" t="n">
+        <v>78721</v>
+      </c>
+      <c r="G90" t="n">
+        <v>4</v>
+      </c>
+      <c r="H90" t="n">
+        <v>153928</v>
+      </c>
+      <c r="I90" t="n">
+        <v>206</v>
+      </c>
+      <c r="J90" t="n">
+        <v>76162</v>
+      </c>
+      <c r="K90" t="n">
+        <v>80715</v>
+      </c>
+      <c r="L90" t="n">
+        <v>3</v>
+      </c>
+      <c r="M90" t="n">
+        <v>156880</v>
+      </c>
+      <c r="N90" t="n">
+        <v>76183</v>
+      </c>
+      <c r="O90" t="n">
+        <v>81176</v>
+      </c>
+      <c r="P90" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>157363</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Duliajan</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Dibrugarh</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>84192</v>
+      </c>
+      <c r="F91" t="n">
+        <v>86943</v>
+      </c>
+      <c r="G91" t="n">
+        <v>3</v>
+      </c>
+      <c r="H91" t="n">
+        <v>171138</v>
+      </c>
+      <c r="I91" t="n">
+        <v>224</v>
+      </c>
+      <c r="J91" t="n">
+        <v>87156</v>
+      </c>
+      <c r="K91" t="n">
+        <v>91761</v>
+      </c>
+      <c r="L91" t="n">
+        <v>3</v>
+      </c>
+      <c r="M91" t="n">
+        <v>178920</v>
+      </c>
+      <c r="N91" t="n">
+        <v>85443</v>
+      </c>
+      <c r="O91" t="n">
+        <v>91178</v>
+      </c>
+      <c r="P91" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>176624</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Tingkhong</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Dibrugarh</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>82131</v>
+      </c>
+      <c r="F92" t="n">
+        <v>86416</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>168547</v>
+      </c>
+      <c r="I92" t="n">
+        <v>214</v>
+      </c>
+      <c r="J92" t="n">
+        <v>84595</v>
+      </c>
+      <c r="K92" t="n">
+        <v>90469</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>175064</v>
+      </c>
+      <c r="N92" t="n">
+        <v>85700</v>
+      </c>
+      <c r="O92" t="n">
+        <v>91958</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>177658</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Naharkatia</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Dibrugarh</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>76044</v>
+      </c>
+      <c r="F93" t="n">
+        <v>78117</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>154162</v>
+      </c>
+      <c r="I93" t="n">
+        <v>210</v>
+      </c>
+      <c r="J93" t="n">
+        <v>76822</v>
+      </c>
+      <c r="K93" t="n">
+        <v>80224</v>
+      </c>
+      <c r="L93" t="n">
+        <v>1</v>
+      </c>
+      <c r="M93" t="n">
+        <v>157047</v>
+      </c>
+      <c r="N93" t="n">
+        <v>76114</v>
+      </c>
+      <c r="O93" t="n">
+        <v>79783</v>
+      </c>
+      <c r="P93" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>155898</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Sonari</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Charaideo</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>84367</v>
+      </c>
+      <c r="F94" t="n">
+        <v>86512</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>170879</v>
+      </c>
+      <c r="I94" t="n">
+        <v>207</v>
+      </c>
+      <c r="J94" t="n">
+        <v>85300</v>
+      </c>
+      <c r="K94" t="n">
+        <v>88382</v>
+      </c>
+      <c r="L94" t="n">
+        <v>1</v>
+      </c>
+      <c r="M94" t="n">
+        <v>173683</v>
+      </c>
+      <c r="N94" t="n">
+        <v>84602</v>
+      </c>
+      <c r="O94" t="n">
+        <v>87252</v>
+      </c>
+      <c r="P94" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>171855</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Mahmora</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Charaideo</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>72496</v>
+      </c>
+      <c r="F95" t="n">
+        <v>75170</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>147667</v>
+      </c>
+      <c r="I95" t="n">
+        <v>184</v>
+      </c>
+      <c r="J95" t="n">
+        <v>73352</v>
+      </c>
+      <c r="K95" t="n">
+        <v>77029</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>150381</v>
+      </c>
+      <c r="N95" t="n">
+        <v>72805</v>
+      </c>
+      <c r="O95" t="n">
+        <v>75889</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>148694</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Demow</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Sibsagar</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>87326</v>
+      </c>
+      <c r="F96" t="n">
+        <v>88992</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>176318</v>
+      </c>
+      <c r="I96" t="n">
+        <v>230</v>
+      </c>
+      <c r="J96" t="n">
+        <v>88004</v>
+      </c>
+      <c r="K96" t="n">
+        <v>91205</v>
+      </c>
+      <c r="L96" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" t="n">
+        <v>179210</v>
+      </c>
+      <c r="N96" t="n">
+        <v>87716</v>
+      </c>
+      <c r="O96" t="n">
+        <v>90673</v>
+      </c>
+      <c r="P96" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>178390</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Sibsagar</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Sibsagar</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>102772</v>
+      </c>
+      <c r="F97" t="n">
+        <v>104832</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" t="n">
+        <v>207605</v>
+      </c>
+      <c r="I97" t="n">
+        <v>278</v>
+      </c>
+      <c r="J97" t="n">
+        <v>103430</v>
+      </c>
+      <c r="K97" t="n">
+        <v>106347</v>
+      </c>
+      <c r="L97" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" t="n">
+        <v>209778</v>
+      </c>
+      <c r="N97" t="n">
+        <v>103484</v>
+      </c>
+      <c r="O97" t="n">
+        <v>106491</v>
+      </c>
+      <c r="P97" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>209976</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Nazira</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Sibsagar</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>87688</v>
+      </c>
+      <c r="F98" t="n">
+        <v>91077</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" t="n">
+        <v>178766</v>
+      </c>
+      <c r="I98" t="n">
+        <v>233</v>
+      </c>
+      <c r="J98" t="n">
+        <v>89070</v>
+      </c>
+      <c r="K98" t="n">
+        <v>94159</v>
+      </c>
+      <c r="L98" t="n">
+        <v>2</v>
+      </c>
+      <c r="M98" t="n">
+        <v>183231</v>
+      </c>
+      <c r="N98" t="n">
+        <v>88645</v>
+      </c>
+      <c r="O98" t="n">
+        <v>93549</v>
+      </c>
+      <c r="P98" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>182196</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Majuli</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Majuli</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>71185</v>
+      </c>
+      <c r="F99" t="n">
+        <v>68684</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>139869</v>
+      </c>
+      <c r="I99" t="n">
+        <v>188</v>
+      </c>
+      <c r="J99" t="n">
+        <v>73227</v>
+      </c>
+      <c r="K99" t="n">
+        <v>71401</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>144628</v>
+      </c>
+      <c r="N99" t="n">
+        <v>73545</v>
+      </c>
+      <c r="O99" t="n">
+        <v>71292</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>144837</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Teok</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Jorhat</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>94545</v>
+      </c>
+      <c r="F100" t="n">
+        <v>97661</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>192206</v>
+      </c>
+      <c r="I100" t="n">
+        <v>249</v>
+      </c>
+      <c r="J100" t="n">
+        <v>96986</v>
+      </c>
+      <c r="K100" t="n">
+        <v>101334</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>198320</v>
+      </c>
+      <c r="N100" t="n">
+        <v>96485</v>
+      </c>
+      <c r="O100" t="n">
+        <v>101479</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>197964</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Jorhat</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Jorhat</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>70894</v>
+      </c>
+      <c r="F101" t="n">
+        <v>75836</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" t="n">
+        <v>146731</v>
+      </c>
+      <c r="I101" t="n">
+        <v>182</v>
+      </c>
+      <c r="J101" t="n">
+        <v>72507</v>
+      </c>
+      <c r="K101" t="n">
+        <v>78417</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>150924</v>
+      </c>
+      <c r="N101" t="n">
+        <v>70897</v>
+      </c>
+      <c r="O101" t="n">
+        <v>77382</v>
+      </c>
+      <c r="P101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>148280</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Mariani</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Jorhat</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>80129</v>
+      </c>
+      <c r="F102" t="n">
+        <v>82413</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>162542</v>
+      </c>
+      <c r="I102" t="n">
+        <v>210</v>
+      </c>
+      <c r="J102" t="n">
+        <v>82907</v>
+      </c>
+      <c r="K102" t="n">
+        <v>86967</v>
+      </c>
+      <c r="L102" t="n">
+        <v>1</v>
+      </c>
+      <c r="M102" t="n">
+        <v>169875</v>
+      </c>
+      <c r="N102" t="n">
+        <v>80156</v>
+      </c>
+      <c r="O102" t="n">
+        <v>84832</v>
+      </c>
+      <c r="P102" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>164989</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Titabor</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Jorhat</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>95350</v>
+      </c>
+      <c r="F103" t="n">
+        <v>100439</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>195789</v>
+      </c>
+      <c r="I103" t="n">
+        <v>245</v>
+      </c>
+      <c r="J103" t="n">
+        <v>98851</v>
+      </c>
+      <c r="K103" t="n">
+        <v>105717</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>204568</v>
+      </c>
+      <c r="N103" t="n">
+        <v>96801</v>
+      </c>
+      <c r="O103" t="n">
+        <v>103713</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>200514</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Golaghat</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Golaghat</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>98983</v>
+      </c>
+      <c r="F104" t="n">
+        <v>101444</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2</v>
+      </c>
+      <c r="H104" t="n">
+        <v>200429</v>
+      </c>
+      <c r="I104" t="n">
+        <v>268</v>
+      </c>
+      <c r="J104" t="n">
+        <v>101441</v>
+      </c>
+      <c r="K104" t="n">
+        <v>105110</v>
+      </c>
+      <c r="L104" t="n">
+        <v>2</v>
+      </c>
+      <c r="M104" t="n">
+        <v>206553</v>
+      </c>
+      <c r="N104" t="n">
+        <v>99458</v>
+      </c>
+      <c r="O104" t="n">
+        <v>101927</v>
+      </c>
+      <c r="P104" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>201387</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Dergaon</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Golaghat</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>85296</v>
+      </c>
+      <c r="F105" t="n">
+        <v>86979</v>
+      </c>
+      <c r="G105" t="n">
+        <v>3</v>
+      </c>
+      <c r="H105" t="n">
+        <v>172278</v>
+      </c>
+      <c r="I105" t="n">
+        <v>235</v>
+      </c>
+      <c r="J105" t="n">
+        <v>87952</v>
+      </c>
+      <c r="K105" t="n">
+        <v>91426</v>
+      </c>
+      <c r="L105" t="n">
+        <v>3</v>
+      </c>
+      <c r="M105" t="n">
+        <v>179381</v>
+      </c>
+      <c r="N105" t="n">
+        <v>87114</v>
+      </c>
+      <c r="O105" t="n">
+        <v>90415</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>177529</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Bokakhat</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Golaghat</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>77452</v>
+      </c>
+      <c r="F106" t="n">
+        <v>79793</v>
+      </c>
+      <c r="G106" t="n">
+        <v>2</v>
+      </c>
+      <c r="H106" t="n">
+        <v>157247</v>
+      </c>
+      <c r="I106" t="n">
+        <v>212</v>
+      </c>
+      <c r="J106" t="n">
+        <v>80667</v>
+      </c>
+      <c r="K106" t="n">
+        <v>85184</v>
+      </c>
+      <c r="L106" t="n">
+        <v>1</v>
+      </c>
+      <c r="M106" t="n">
+        <v>165852</v>
+      </c>
+      <c r="N106" t="n">
+        <v>79952</v>
+      </c>
+      <c r="O106" t="n">
+        <v>84695</v>
+      </c>
+      <c r="P106" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>164648</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Khumtai</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Golaghat</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>80952</v>
+      </c>
+      <c r="F107" t="n">
+        <v>83192</v>
+      </c>
+      <c r="G107" t="n">
+        <v>4</v>
+      </c>
+      <c r="H107" t="n">
+        <v>164148</v>
+      </c>
+      <c r="I107" t="n">
+        <v>230</v>
+      </c>
+      <c r="J107" t="n">
+        <v>84342</v>
+      </c>
+      <c r="K107" t="n">
+        <v>88469</v>
+      </c>
+      <c r="L107" t="n">
+        <v>5</v>
+      </c>
+      <c r="M107" t="n">
+        <v>172816</v>
+      </c>
+      <c r="N107" t="n">
+        <v>84124</v>
+      </c>
+      <c r="O107" t="n">
+        <v>87568</v>
+      </c>
+      <c r="P107" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>171697</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Sarupathar</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Golaghat</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>96543</v>
+      </c>
+      <c r="F108" t="n">
+        <v>95604</v>
+      </c>
+      <c r="G108" t="n">
+        <v>3</v>
+      </c>
+      <c r="H108" t="n">
+        <v>192150</v>
+      </c>
+      <c r="I108" t="n">
+        <v>213</v>
+      </c>
+      <c r="J108" t="n">
+        <v>98870</v>
+      </c>
+      <c r="K108" t="n">
+        <v>99210</v>
+      </c>
+      <c r="L108" t="n">
+        <v>2</v>
+      </c>
+      <c r="M108" t="n">
+        <v>198082</v>
+      </c>
+      <c r="N108" t="n">
+        <v>94114</v>
+      </c>
+      <c r="O108" t="n">
+        <v>93280</v>
+      </c>
+      <c r="P108" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>187396</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Bokajan</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Karbi Anglong</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>75168</v>
+      </c>
+      <c r="F109" t="n">
+        <v>75032</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>150200</v>
+      </c>
+      <c r="I109" t="n">
+        <v>214</v>
+      </c>
+      <c r="J109" t="n">
+        <v>78627</v>
+      </c>
+      <c r="K109" t="n">
+        <v>79575</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>158202</v>
+      </c>
+      <c r="N109" t="n">
+        <v>78054</v>
+      </c>
+      <c r="O109" t="n">
+        <v>79187</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>157241</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Howraghat</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Karbi Anglong</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>91393</v>
+      </c>
+      <c r="F110" t="n">
+        <v>93449</v>
+      </c>
+      <c r="G110" t="n">
+        <v>6</v>
+      </c>
+      <c r="H110" t="n">
+        <v>184848</v>
+      </c>
+      <c r="I110" t="n">
+        <v>239</v>
+      </c>
+      <c r="J110" t="n">
+        <v>95868</v>
+      </c>
+      <c r="K110" t="n">
+        <v>99110</v>
+      </c>
+      <c r="L110" t="n">
+        <v>5</v>
+      </c>
+      <c r="M110" t="n">
+        <v>194983</v>
+      </c>
+      <c r="N110" t="n">
+        <v>93420</v>
+      </c>
+      <c r="O110" t="n">
+        <v>96191</v>
+      </c>
+      <c r="P110" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>189616</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Diphu</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Karbi Anglong</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>87918</v>
+      </c>
+      <c r="F111" t="n">
+        <v>89346</v>
+      </c>
+      <c r="G111" t="n">
+        <v>12</v>
+      </c>
+      <c r="H111" t="n">
+        <v>177276</v>
+      </c>
+      <c r="I111" t="n">
+        <v>237</v>
+      </c>
+      <c r="J111" t="n">
+        <v>92327</v>
+      </c>
+      <c r="K111" t="n">
+        <v>94565</v>
+      </c>
+      <c r="L111" t="n">
+        <v>11</v>
+      </c>
+      <c r="M111" t="n">
+        <v>186903</v>
+      </c>
+      <c r="N111" t="n">
+        <v>89691</v>
+      </c>
+      <c r="O111" t="n">
+        <v>92439</v>
+      </c>
+      <c r="P111" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>182139</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Rongkhang</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>West Karbi Anglong</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>64863</v>
+      </c>
+      <c r="F112" t="n">
+        <v>63800</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="n">
+        <v>128664</v>
+      </c>
+      <c r="I112" t="n">
+        <v>193</v>
+      </c>
+      <c r="J112" t="n">
+        <v>66636</v>
+      </c>
+      <c r="K112" t="n">
+        <v>66221</v>
+      </c>
+      <c r="L112" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" t="n">
+        <v>132858</v>
+      </c>
+      <c r="N112" t="n">
+        <v>66358</v>
+      </c>
+      <c r="O112" t="n">
+        <v>65499</v>
+      </c>
+      <c r="P112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>131858</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Amri</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>West Karbi Anglong</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>48415</v>
+      </c>
+      <c r="F113" t="n">
+        <v>48127</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>96542</v>
+      </c>
+      <c r="I113" t="n">
+        <v>165</v>
+      </c>
+      <c r="J113" t="n">
+        <v>50019</v>
+      </c>
+      <c r="K113" t="n">
+        <v>50300</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>100319</v>
+      </c>
+      <c r="N113" t="n">
+        <v>49919</v>
+      </c>
+      <c r="O113" t="n">
+        <v>50178</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>100097</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Haflong</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Dima Hasao</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>77327</v>
+      </c>
+      <c r="F114" t="n">
+        <v>77932</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>155259</v>
+      </c>
+      <c r="I114" t="n">
+        <v>261</v>
+      </c>
+      <c r="J114" t="n">
+        <v>78641</v>
+      </c>
+      <c r="K114" t="n">
+        <v>80132</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>158773</v>
+      </c>
+      <c r="N114" t="n">
+        <v>78279</v>
+      </c>
+      <c r="O114" t="n">
+        <v>79925</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>158204</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Lakhipur</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Cachar</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>84209</v>
+      </c>
+      <c r="F115" t="n">
+        <v>83992</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" t="n">
+        <v>168202</v>
+      </c>
+      <c r="I115" t="n">
+        <v>222</v>
+      </c>
+      <c r="J115" t="n">
+        <v>87264</v>
+      </c>
+      <c r="K115" t="n">
+        <v>89347</v>
+      </c>
+      <c r="L115" t="n">
+        <v>1</v>
+      </c>
+      <c r="M115" t="n">
+        <v>176612</v>
+      </c>
+      <c r="N115" t="n">
+        <v>87611</v>
+      </c>
+      <c r="O115" t="n">
+        <v>89597</v>
+      </c>
+      <c r="P115" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>177209</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Udharbond</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Cachar</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>90863</v>
+      </c>
+      <c r="F116" t="n">
+        <v>93507</v>
+      </c>
+      <c r="G116" t="n">
+        <v>2</v>
+      </c>
+      <c r="H116" t="n">
+        <v>184372</v>
+      </c>
+      <c r="I116" t="n">
+        <v>231</v>
+      </c>
+      <c r="J116" t="n">
+        <v>94248</v>
+      </c>
+      <c r="K116" t="n">
+        <v>99188</v>
+      </c>
+      <c r="L116" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" t="n">
+        <v>193437</v>
+      </c>
+      <c r="N116" t="n">
+        <v>91303</v>
+      </c>
+      <c r="O116" t="n">
+        <v>93564</v>
+      </c>
+      <c r="P116" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>184868</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Katigorah</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Cachar</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>106385</v>
+      </c>
+      <c r="F117" t="n">
+        <v>103269</v>
+      </c>
+      <c r="G117" t="n">
+        <v>4</v>
+      </c>
+      <c r="H117" t="n">
+        <v>209658</v>
+      </c>
+      <c r="I117" t="n">
+        <v>281</v>
+      </c>
+      <c r="J117" t="n">
+        <v>110460</v>
+      </c>
+      <c r="K117" t="n">
+        <v>108724</v>
+      </c>
+      <c r="L117" t="n">
+        <v>1</v>
+      </c>
+      <c r="M117" t="n">
+        <v>219185</v>
+      </c>
+      <c r="N117" t="n">
+        <v>108454</v>
+      </c>
+      <c r="O117" t="n">
+        <v>104776</v>
+      </c>
+      <c r="P117" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>213231</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Borkhola</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Cachar</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>100634</v>
+      </c>
+      <c r="F118" t="n">
+        <v>98517</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" t="n">
+        <v>199152</v>
+      </c>
+      <c r="I118" t="n">
+        <v>258</v>
+      </c>
+      <c r="J118" t="n">
+        <v>104263</v>
+      </c>
+      <c r="K118" t="n">
+        <v>103988</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>208251</v>
+      </c>
+      <c r="N118" t="n">
+        <v>103938</v>
+      </c>
+      <c r="O118" t="n">
+        <v>100783</v>
+      </c>
+      <c r="P118" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>204723</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Silchar</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Cachar</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>103972</v>
+      </c>
+      <c r="F119" t="n">
+        <v>109404</v>
+      </c>
+      <c r="G119" t="n">
+        <v>10</v>
+      </c>
+      <c r="H119" t="n">
+        <v>213386</v>
+      </c>
+      <c r="I119" t="n">
+        <v>257</v>
+      </c>
+      <c r="J119" t="n">
+        <v>107769</v>
+      </c>
+      <c r="K119" t="n">
+        <v>114572</v>
+      </c>
+      <c r="L119" t="n">
+        <v>10</v>
+      </c>
+      <c r="M119" t="n">
+        <v>222351</v>
+      </c>
+      <c r="N119" t="n">
+        <v>103040</v>
+      </c>
+      <c r="O119" t="n">
+        <v>108493</v>
+      </c>
+      <c r="P119" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>211538</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Sonai</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Cachar</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>94011</v>
+      </c>
+      <c r="F120" t="n">
+        <v>91936</v>
+      </c>
+      <c r="G120" t="n">
+        <v>5</v>
+      </c>
+      <c r="H120" t="n">
+        <v>185952</v>
+      </c>
+      <c r="I120" t="n">
+        <v>244</v>
+      </c>
+      <c r="J120" t="n">
+        <v>98201</v>
+      </c>
+      <c r="K120" t="n">
+        <v>97860</v>
+      </c>
+      <c r="L120" t="n">
+        <v>4</v>
+      </c>
+      <c r="M120" t="n">
+        <v>196065</v>
+      </c>
+      <c r="N120" t="n">
+        <v>98370</v>
+      </c>
+      <c r="O120" t="n">
+        <v>96178</v>
+      </c>
+      <c r="P120" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>194551</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Dholai</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Cachar</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>96257</v>
+      </c>
+      <c r="F121" t="n">
+        <v>94516</v>
+      </c>
+      <c r="G121" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" t="n">
+        <v>190774</v>
+      </c>
+      <c r="I121" t="n">
+        <v>239</v>
+      </c>
+      <c r="J121" t="n">
+        <v>99683</v>
+      </c>
+      <c r="K121" t="n">
+        <v>99854</v>
+      </c>
+      <c r="L121" t="n">
+        <v>1</v>
+      </c>
+      <c r="M121" t="n">
+        <v>199538</v>
+      </c>
+      <c r="N121" t="n">
+        <v>98891</v>
+      </c>
+      <c r="O121" t="n">
+        <v>96892</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>195783</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Hailakandi</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Hailakandi</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>108746</v>
+      </c>
+      <c r="F122" t="n">
+        <v>103139</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" t="n">
+        <v>211886</v>
+      </c>
+      <c r="I122" t="n">
+        <v>284</v>
+      </c>
+      <c r="J122" t="n">
+        <v>112226</v>
+      </c>
+      <c r="K122" t="n">
+        <v>108537</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>220763</v>
+      </c>
+      <c r="N122" t="n">
+        <v>112704</v>
+      </c>
+      <c r="O122" t="n">
+        <v>107357</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>220061</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Algapur-Katlicherra</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Hailakandi</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>136925</v>
+      </c>
+      <c r="F123" t="n">
+        <v>122337</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>259262</v>
+      </c>
+      <c r="I123" t="n">
+        <v>339</v>
+      </c>
+      <c r="J123" t="n">
+        <v>143279</v>
+      </c>
+      <c r="K123" t="n">
+        <v>130836</v>
+      </c>
+      <c r="L123" t="n">
+        <v>1</v>
+      </c>
+      <c r="M123" t="n">
+        <v>274116</v>
+      </c>
+      <c r="N123" t="n">
+        <v>144957</v>
+      </c>
+      <c r="O123" t="n">
+        <v>131942</v>
+      </c>
+      <c r="P123" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>276901</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Karimganj North</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Sribhumi</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>130828</v>
+      </c>
+      <c r="F124" t="n">
+        <v>129526</v>
+      </c>
+      <c r="G124" t="n">
+        <v>4</v>
+      </c>
+      <c r="H124" t="n">
+        <v>260358</v>
+      </c>
+      <c r="I124" t="n">
+        <v>326</v>
+      </c>
+      <c r="J124" t="n">
+        <v>137052</v>
+      </c>
+      <c r="K124" t="n">
+        <v>135864</v>
+      </c>
+      <c r="L124" t="n">
+        <v>1</v>
+      </c>
+      <c r="M124" t="n">
+        <v>272917</v>
+      </c>
+      <c r="N124" t="n">
+        <v>132442</v>
+      </c>
+      <c r="O124" t="n">
+        <v>127201</v>
+      </c>
+      <c r="P124" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>259644</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Karimganj South</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Sribhumi</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>141014</v>
+      </c>
+      <c r="F125" t="n">
+        <v>133467</v>
+      </c>
+      <c r="G125" t="n">
+        <v>4</v>
+      </c>
+      <c r="H125" t="n">
+        <v>274485</v>
+      </c>
+      <c r="I125" t="n">
+        <v>356</v>
+      </c>
+      <c r="J125" t="n">
+        <v>149594</v>
+      </c>
+      <c r="K125" t="n">
+        <v>141659</v>
+      </c>
+      <c r="L125" t="n">
+        <v>3</v>
+      </c>
+      <c r="M125" t="n">
+        <v>291256</v>
+      </c>
+      <c r="N125" t="n">
+        <v>147904</v>
+      </c>
+      <c r="O125" t="n">
+        <v>136501</v>
+      </c>
+      <c r="P125" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>284408</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Patharkandi</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Sribhumi</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>90010</v>
+      </c>
+      <c r="F126" t="n">
+        <v>87217</v>
+      </c>
+      <c r="G126" t="n">
+        <v>4</v>
+      </c>
+      <c r="H126" t="n">
+        <v>177231</v>
+      </c>
+      <c r="I126" t="n">
+        <v>228</v>
+      </c>
+      <c r="J126" t="n">
+        <v>93972</v>
+      </c>
+      <c r="K126" t="n">
+        <v>91533</v>
+      </c>
+      <c r="L126" t="n">
+        <v>4</v>
+      </c>
+      <c r="M126" t="n">
+        <v>185509</v>
+      </c>
+      <c r="N126" t="n">
+        <v>91421</v>
+      </c>
+      <c r="O126" t="n">
+        <v>88776</v>
+      </c>
+      <c r="P126" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>180201</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Ram Krishna Nagar</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Sribhumi</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>107956</v>
+      </c>
+      <c r="F127" t="n">
+        <v>103915</v>
+      </c>
+      <c r="G127" t="n">
+        <v>3</v>
+      </c>
+      <c r="H127" t="n">
+        <v>211874</v>
+      </c>
+      <c r="I127" t="n">
+        <v>277</v>
+      </c>
+      <c r="J127" t="n">
+        <v>112948</v>
+      </c>
+      <c r="K127" t="n">
+        <v>109283</v>
+      </c>
+      <c r="L127" t="n">
+        <v>3</v>
+      </c>
+      <c r="M127" t="n">
+        <v>222234</v>
+      </c>
+      <c r="N127" t="n">
+        <v>110669</v>
+      </c>
+      <c r="O127" t="n">
+        <v>105723</v>
+      </c>
+      <c r="P127" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>216396</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5112,7 +12820,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5759,7 +13467,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6045,7 +13753,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6253,7 +13961,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6408,7 +14116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7345,327 +15053,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>page_or_para</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>detention_centres_2019</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Lok Sabha USQ 2340, 03.12.2019, MHA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>inmates_total_20191128</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>970</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Lok Sabha USQ 2340, 03.12.2019, MHA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>table, Total row</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>inmates_men_20191128</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>646</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Total row</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>inmates_women_20191128</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>324</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Total row</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>capacity_total_2020</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3331</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Lok Sabha USQ 3880, 17.03.2020, MHA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>answer, Total row</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>matia_goalpara_capacity_under_construction_2020</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Lok Sabha USQ 3880, 17.03.2020, MHA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>answer page 2</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>inmates_died_20190301_20200229</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>10</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Lok Sabha USQ 3880, 17.03.2020, MHA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>answer page 2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>declared_foreigners_over_3_years_in_detention_2019</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>181</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Lok Sabha USQ 3561, 10.12.2019, MHA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>answer (a)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>convicted_foreigners_over_3_years_in_detention_2019</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>44</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>answer (a)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>declared_foreigners_detained_in_2019</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>289</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>answer (b)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>released_after_3_years_per_sc_10052019</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>128</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>answer (d)&amp;(e)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/downloads/assam.xlsx
+++ b/downloads/assam.xlsx
@@ -12957,7 +12957,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BLO visits each household with a pre-filled register (Statement-1) of existing electors to verify or correct; at least three visits to a locked house</t>
+          <t>BLO visits each household with a pre-filled register (Statement-1) of existing electors to verify or correct. At least three visits to a locked house</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Every elector given a pre-printed enumeration form to fill, sign and return; a name whose form is not returned is left off the draft</t>
+          <t>Every elector given a pre-printed enumeration form to fill, sign and return. A name whose form is not returned is left off the draft</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>None. The order names no enumeration form; the BLO fills Statement-1 (existing electors), Statement-2 (un-enrolled eligible citizens) and Statement-3 (prospective electors) and gets Form 6, 7 or 8 filled where needed</t>
+          <t>None. The order names no enumeration form. The BLO fills Statement-1 (existing electors), Statement-2 (un-enrolled eligible citizens) and Statement-3 (prospective electors) and gets Form 6, 7 or 8 filled where needed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -13051,7 +13051,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No document during enumeration; after the draft, notices to electors not linked with the last SIR roll, who then show documents from the list (11 documents, Aadhaar, Bihar SIR extract)</t>
+          <t>No document during enumeration. After the draft, notices to electors not linked with the last SIR roll, who then show documents from the list (11 documents, Aadhaar, Bihar SIR extract)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -13105,7 +13105,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kept out of the verification register; carried forward to the draft unchanged; removed or changed only on an order of a Foreigners Tribunal or a court</t>
+          <t>Kept out of the verification register. Carried forward to the draft unchanged. Removed or changed only on an order of a Foreigners Tribunal or a court</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Form 6 as in an ordinary revision; Aadhaar voluntary</t>
+          <t>Form 6 as in an ordinary revision. Aadhaar voluntary</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Form 6 with a Declaration Form (Annexure IV) asking for last-SIR roll details; documents on notice by birth cohort</t>
+          <t>Form 6 with a Declaration Form (Annexure IV) asking for last-SIR roll details. Documents on notice by birth cohort</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -13253,7 +13253,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Death deletions need certificate or Form 7; shifting needs Form 8; ERO cross-checks polling stations with deletions over 2% and objectors with more than 5 objections; 10% field check of non-death deletions</t>
+          <t>Death deletions need certificate or Form 7. Shifting needs Form 8. ERO cross-checks polling stations with deletions over 2% and objectors with more than 5 objections. 10% field check of non-death deletions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ERO/AERO may not delete a draft entry without a fair and reasonable opportunity; personal notice for proposed deletion other than death</t>
+          <t>ERO/AERO may not delete a draft entry without a fair and reasonable opportunity. Personal notice for proposed deletion other than death</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -13322,7 +13322,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Not printed for parties; generated and kept by EROs</t>
+          <t>Not printed for parties. Generated and kept by EROs</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A BLA may file no more than 10 forms a day; over 30 in the claims period, the ERO or AERO cross-verifies them</t>
+          <t>A BLA may file no more than 10 forms a day. Over 30 in the claims period, the ERO or AERO cross-verifies them</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">

--- a/downloads/assam.xlsx
+++ b/downloads/assam.xlsx
@@ -13105,7 +13105,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kept out of the verification register. Carried forward to the draft unchanged. Removed or changed only on an order of a Foreigners Tribunal or a court</t>
+          <t>Kept out of the verification register. Carried forward to the draft unchanged. Deleted or changed only on an order of a Foreigners Tribunal or a court</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Multiple entries, dead and permanently shifted electors removed through Form 7 before the draft</t>
+          <t>Multiple entries, dead and permanently shifted electors deleted through Form 7 before the draft</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
